--- a/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0001T0006Z000C1N3_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0001T0006Z000C1N3_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>39.2281718433649</v>
       </c>
       <c r="E2" t="n">
-        <v>17.23463731829802</v>
+        <v>24.9685611533497</v>
       </c>
       <c r="F2" t="n">
-        <v>17.2619647282024</v>
+        <v>24.96494334865256</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,10 +518,10 @@
         <v>73.75210129976971</v>
       </c>
       <c r="E3" t="n">
-        <v>17.23463731829802</v>
+        <v>24.9685611533497</v>
       </c>
       <c r="F3" t="n">
-        <v>17.2619647282024</v>
+        <v>24.96494334865256</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -529,6 +529,38 @@
         </is>
       </c>
       <c r="H3" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>W0051F0001T0006Z000C1N3.png</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>12.73140573830911</v>
+      </c>
+      <c r="D4" t="n">
+        <v>12.7786792065545</v>
+      </c>
+      <c r="E4" t="n">
+        <v>24.9685611533497</v>
+      </c>
+      <c r="F4" t="n">
+        <v>24.96494334865256</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>T1791</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0001T0006Z000C1N3_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791_W0051F0001T0006Z000C1N3_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.24985444635584</v>
+        <v>6.378101347532824</v>
       </c>
       <c r="D2" t="n">
-        <v>39.2281718433649</v>
+        <v>6.374577924546797</v>
       </c>
       <c r="E2" t="n">
-        <v>24.9685611533497</v>
+        <v>4.057391187419326</v>
       </c>
       <c r="F2" t="n">
-        <v>24.96494334865256</v>
+        <v>4.056803294156042</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>73.71912908295188</v>
+        <v>11.97935847597968</v>
       </c>
       <c r="D3" t="n">
-        <v>73.75210129976971</v>
+        <v>11.98471646121258</v>
       </c>
       <c r="E3" t="n">
-        <v>24.9685611533497</v>
+        <v>4.057391187419326</v>
       </c>
       <c r="F3" t="n">
-        <v>24.96494334865256</v>
+        <v>4.056803294156042</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>12.73140573830911</v>
+        <v>2.068853432475231</v>
       </c>
       <c r="D4" t="n">
-        <v>12.7786792065545</v>
+        <v>2.076535371065106</v>
       </c>
       <c r="E4" t="n">
-        <v>24.9685611533497</v>
+        <v>4.057391187419326</v>
       </c>
       <c r="F4" t="n">
-        <v>24.96494334865256</v>
+        <v>4.056803294156042</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
